--- a/frontend/public/Bills_real.xlsx
+++ b/frontend/public/Bills_real.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="SHREEYA" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="SHREEYA_2" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t xml:space="preserve">AMBE SERVICE</t>
   </si>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Name &amp; Add of Party</t>
   </si>
   <si>
-    <t xml:space="preserve">Billing Period :1st to 31st November  2025</t>
+    <t xml:space="preserve">Billing Period :1st to 30st November  2025</t>
   </si>
   <si>
     <t xml:space="preserve">Shrreeya Developers</t>
@@ -87,6 +87,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Amount </t>
     </r>
@@ -105,7 +106,10 @@
     <t xml:space="preserve">Housekeeping</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">Housekeeping Overtime(in Hrs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 hrs</t>
   </si>
   <si>
     <t xml:space="preserve">Material Charges</t>
@@ -181,6 +185,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -264,7 +269,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -336,13 +341,6 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right style="thin"/>
       <top/>
@@ -389,276 +387,260 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="64">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -845,152 +827,141 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="9"/>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11" t="s">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="15"/>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="16"/>
-      <c r="H9" s="17"/>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="16"/>
-      <c r="H10" s="17"/>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="17"/>
+      <c r="G9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="17"/>
+      <c r="G10" s="18"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="22"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
@@ -1002,9 +973,8 @@
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
       <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23"/>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
@@ -1012,9 +982,8 @@
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
       <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
         <v>14</v>
       </c>
@@ -1030,390 +999,372 @@
       <c r="E14" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="25"/>
-      <c r="G14" s="24" t="s">
+      <c r="F14" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="26" t="s">
+      <c r="G14" s="26" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24"/>
       <c r="B15" s="24"/>
       <c r="C15" s="24"/>
       <c r="D15" s="24"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="29"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="30" t="n">
+      <c r="E15" s="25"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="26"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="30" t="n">
+      <c r="C16" s="27" t="n">
         <v>9985</v>
       </c>
-      <c r="D16" s="31" t="n">
+      <c r="D16" s="28" t="n">
         <v>12500</v>
       </c>
-      <c r="E16" s="32" t="n">
+      <c r="E16" s="29" t="n">
         <v>156</v>
       </c>
-      <c r="F16" s="32"/>
-      <c r="G16" s="33" t="n">
+      <c r="F16" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="34" t="n">
+      <c r="G16" s="28" t="n">
         <f aca="false">E16*(D16/30)</f>
         <v>65000</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="35"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="38"/>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="39"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="17"/>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>9985</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <f aca="false">D16/30/9</f>
+        <v>46.2962962962963</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="28"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="33"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="34"/>
       <c r="G18" s="36"/>
-      <c r="H18" s="38"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="39"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="17"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="33"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="34"/>
       <c r="G19" s="36"/>
-      <c r="H19" s="38"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="17"/>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="17"/>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="36"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="44" t="n">
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="34"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="34"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="34"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="39" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="36"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="44" t="n">
-        <f aca="false">H16+H22</f>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="34"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="39" t="n">
+        <f aca="false">G16+G22</f>
         <v>65000</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="46"/>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="44" t="n">
-        <f aca="false">H23*15%</f>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="41"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="39" t="n">
+        <f aca="false">G23*15%</f>
         <v>9750</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="47"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="49"/>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="50" t="s">
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="44"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="51" t="n">
-        <f aca="false">SUM(H23+H24)</f>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="46" t="n">
+        <f aca="false">SUM(G23+G24)</f>
         <v>74750</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="54"/>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="52" t="s">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="52"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="55" t="s">
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="49"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="56" t="n">
-        <f aca="false">H26*9%</f>
+      <c r="B28" s="47"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="51" t="n">
+        <f aca="false">G26*9%</f>
         <v>6727.5</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="55" t="s">
+      <c r="A29" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="55"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="55"/>
-      <c r="H29" s="31" t="n">
-        <f aca="false">H26*9%</f>
+      <c r="B29" s="42"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="28" t="n">
+        <f aca="false">G26*9%</f>
         <v>6727.5</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
-      <c r="C30" s="47"/>
-      <c r="H30" s="36"/>
-    </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="52" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="41"/>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="58"/>
-      <c r="B32" s="58"/>
-      <c r="C32" s="58"/>
-      <c r="D32" s="59" t="s">
+      <c r="A30" s="42"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="42"/>
+      <c r="G30" s="34"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="60" t="n">
-        <f aca="false">SUM(H26+H28+H29)</f>
+      <c r="B31" s="47"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="53"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="54"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="56" t="n">
+        <f aca="false">SUM(G26+G28+G29)</f>
         <v>88205</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="58"/>
-      <c r="C33" s="58"/>
-      <c r="D33" s="61" t="s">
+      <c r="A33" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="62" t="n">
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="58" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="63"/>
-      <c r="B34" s="64"/>
-      <c r="C34" s="65"/>
-      <c r="D34" s="66" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" s="66"/>
-      <c r="F34" s="66"/>
-      <c r="G34" s="66"/>
-      <c r="H34" s="56" t="n">
-        <f aca="false">H32-H33</f>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="59"/>
+      <c r="B34" s="60"/>
+      <c r="C34" s="61"/>
+      <c r="D34" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="62"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="51" t="n">
+        <f aca="false">G32-G33</f>
         <v>88205</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35" s="23"/>
       <c r="C35" s="23"/>
-      <c r="D35" s="67" t="s">
-        <v>40</v>
-      </c>
-      <c r="E35" s="67"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="67"/>
-      <c r="H35" s="67"/>
-    </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D35" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="23"/>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
-    </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D36" s="63"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="63"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="23"/>
       <c r="B37" s="23"/>
       <c r="C37" s="23"/>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
-      <c r="H37" s="67"/>
-    </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="23"/>
       <c r="B38" s="23"/>
       <c r="C38" s="23"/>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="67"/>
-    </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D38" s="63"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="63"/>
+      <c r="G38" s="63"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="23"/>
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
-      <c r="H39" s="67"/>
+      <c r="D39" s="63"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="63"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="F7:H7"/>
+  <mergeCells count="46">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:G7"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:H13"/>
+    <mergeCell ref="A12:G13"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
     <mergeCell ref="G14:G15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D25:F25"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D26:F26"/>
     <mergeCell ref="A27:C27"/>
-    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D27:F27"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D28:F28"/>
     <mergeCell ref="A29:C30"/>
-    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D29:F29"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D31:F31"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D32:F32"/>
     <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
     <mergeCell ref="A35:C39"/>
-    <mergeCell ref="D35:H39"/>
+    <mergeCell ref="D35:G39"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
